--- a/Leitor_de_Fatura/Faturas_Analaiser/Relatorio_Consolidado_NEOENERGIA_Texter.xlsx
+++ b/Leitor_de_Fatura/Faturas_Analaiser/Relatorio_Consolidado_NEOENERGIA_Texter.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Base_Vazia" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Classificação" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Consumo_Faturado" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Consumo_Medido" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
@@ -429,8 +429,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -456,8 +456,14 @@
           <t>12540</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" s="1" t="inlineStr"/>
+      <c r="B2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -465,8 +471,14 @@
           <t>12541</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr"/>
-      <c r="C3" s="1" t="inlineStr"/>
+      <c r="B3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -474,8 +486,14 @@
           <t>12555</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr"/>
-      <c r="C4" s="1" t="inlineStr"/>
+      <c r="B4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -483,8 +501,14 @@
           <t>13353</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr"/>
-      <c r="C5" s="1" t="inlineStr"/>
+      <c r="B5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -492,8 +516,14 @@
           <t>15882</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr"/>
-      <c r="C6" s="1" t="inlineStr"/>
+      <c r="B6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -501,8 +531,14 @@
           <t>2018412</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr"/>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -510,8 +546,14 @@
           <t>2053104</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr"/>
-      <c r="C8" s="1" t="inlineStr"/>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -519,8 +561,14 @@
           <t>2110544</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr"/>
-      <c r="C9" s="1" t="inlineStr"/>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -528,8 +576,14 @@
           <t>2132268</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr"/>
-      <c r="C10" s="1" t="inlineStr"/>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO -  AGUA, ESGOTO E SANEAMENTO</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -537,8 +591,14 @@
           <t>2134459</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr"/>
-      <c r="C11" s="1" t="inlineStr"/>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -546,8 +606,14 @@
           <t>2202090</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr"/>
-      <c r="C12" s="1" t="inlineStr"/>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -555,8 +621,14 @@
           <t>2223789</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr"/>
-      <c r="C13" s="1" t="inlineStr"/>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -564,8 +636,14 @@
           <t>2343276</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr"/>
-      <c r="C14" s="1" t="inlineStr"/>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -573,8 +651,14 @@
           <t>2355522</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr"/>
-      <c r="C15" s="1" t="inlineStr"/>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -582,8 +666,14 @@
           <t>2380786</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr"/>
-      <c r="C16" s="1" t="inlineStr"/>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -591,8 +681,14 @@
           <t>2389523</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr"/>
-      <c r="C17" s="1" t="inlineStr"/>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -600,8 +696,14 @@
           <t>241381</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr"/>
-      <c r="C18" s="1" t="inlineStr"/>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -609,8 +711,14 @@
           <t>241397</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr"/>
-      <c r="C19" s="1" t="inlineStr"/>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO -  AGUA, ESGOTO E SANEAMENTO</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -618,8 +726,14 @@
           <t>241512</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr"/>
-      <c r="C20" s="1" t="inlineStr"/>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -627,8 +741,14 @@
           <t>2451149</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr"/>
-      <c r="C21" s="1" t="inlineStr"/>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -636,8 +756,14 @@
           <t>2511772</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr"/>
-      <c r="C22" s="1" t="inlineStr"/>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -645,8 +771,14 @@
           <t>2531339</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr"/>
-      <c r="C23" s="1" t="inlineStr"/>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -654,8 +786,14 @@
           <t>2556689</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr"/>
-      <c r="C24" s="1" t="inlineStr"/>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO -  AGUA, ESGOTO E SANEAMENTO</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -663,8 +801,14 @@
           <t>2607837</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr"/>
-      <c r="C25" s="1" t="inlineStr"/>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO -  AGUA, ESGOTO E SANEAMENTO</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -672,8 +816,14 @@
           <t>271229</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr"/>
-      <c r="C26" s="1" t="inlineStr"/>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -681,8 +831,14 @@
           <t>271246</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr"/>
-      <c r="C27" s="1" t="inlineStr"/>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -690,8 +846,14 @@
           <t>271617</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr"/>
-      <c r="C28" s="1" t="inlineStr"/>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -699,8 +861,14 @@
           <t>271921</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr"/>
-      <c r="C29" s="1" t="inlineStr"/>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -708,8 +876,14 @@
           <t>272050</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr"/>
-      <c r="C30" s="1" t="inlineStr"/>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -717,8 +891,14 @@
           <t>272272</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr"/>
-      <c r="C31" s="1" t="inlineStr"/>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -726,8 +906,14 @@
           <t>272393</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr"/>
-      <c r="C32" s="1" t="inlineStr"/>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -735,8 +921,14 @@
           <t>272441</t>
         </is>
       </c>
-      <c r="B33" s="1" t="inlineStr"/>
-      <c r="C33" s="1" t="inlineStr"/>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -744,8 +936,14 @@
           <t>272494</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr"/>
-      <c r="C34" s="1" t="inlineStr"/>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -753,8 +951,14 @@
           <t>272875</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr"/>
-      <c r="C35" s="1" t="inlineStr"/>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -762,8 +966,14 @@
           <t>273017</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr"/>
-      <c r="C36" s="1" t="inlineStr"/>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -771,8 +981,14 @@
           <t>2730374</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr"/>
-      <c r="C37" s="1" t="inlineStr"/>
+      <c r="B37" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -780,8 +996,14 @@
           <t>273264</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr"/>
-      <c r="C38" s="1" t="inlineStr"/>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -789,8 +1011,14 @@
           <t>273313</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr"/>
-      <c r="C39" s="1" t="inlineStr"/>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -798,8 +1026,14 @@
           <t>273617</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr"/>
-      <c r="C40" s="1" t="inlineStr"/>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -807,8 +1041,14 @@
           <t>273705</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr"/>
-      <c r="C41" s="1" t="inlineStr"/>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO -  AGUA, ESGOTO E SANEAMENTO</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -816,8 +1056,14 @@
           <t>273849</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr"/>
-      <c r="C42" s="1" t="inlineStr"/>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -825,8 +1071,14 @@
           <t>274088</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr"/>
-      <c r="C43" s="1" t="inlineStr"/>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -834,8 +1086,14 @@
           <t>274095</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr"/>
-      <c r="C44" s="1" t="inlineStr"/>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -843,8 +1101,14 @@
           <t>274597</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr"/>
-      <c r="C45" s="1" t="inlineStr"/>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -852,8 +1116,14 @@
           <t>274650</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr"/>
-      <c r="C46" s="1" t="inlineStr"/>
+      <c r="B46" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -861,8 +1131,14 @@
           <t>274651</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr"/>
-      <c r="C47" s="1" t="inlineStr"/>
+      <c r="B47" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -870,8 +1146,14 @@
           <t>274679</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr"/>
-      <c r="C48" s="1" t="inlineStr"/>
+      <c r="B48" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
@@ -879,8 +1161,14 @@
           <t>275281</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr"/>
-      <c r="C49" s="1" t="inlineStr"/>
+      <c r="B49" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
@@ -888,8 +1176,14 @@
           <t>275608</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr"/>
-      <c r="C50" s="1" t="inlineStr"/>
+      <c r="B50" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO -  AGUA, ESGOTO E SANEAMENTO</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -897,8 +1191,14 @@
           <t>275779</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr"/>
-      <c r="C51" s="1" t="inlineStr"/>
+      <c r="B51" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
@@ -906,8 +1206,14 @@
           <t>275827</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr"/>
-      <c r="C52" s="1" t="inlineStr"/>
+      <c r="B52" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -915,8 +1221,14 @@
           <t>275900</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr"/>
-      <c r="C53" s="1" t="inlineStr"/>
+      <c r="B53" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
@@ -924,8 +1236,14 @@
           <t>276172</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr"/>
-      <c r="C54" s="1" t="inlineStr"/>
+      <c r="B54" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
@@ -933,8 +1251,14 @@
           <t>276269</t>
         </is>
       </c>
-      <c r="B55" s="1" t="inlineStr"/>
-      <c r="C55" s="1" t="inlineStr"/>
+      <c r="B55" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -942,8 +1266,14 @@
           <t>276409</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr"/>
-      <c r="C56" s="1" t="inlineStr"/>
+      <c r="B56" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO -  AGUA, ESGOTO E SANEAMENTO</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
@@ -951,8 +1281,14 @@
           <t>276537</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr"/>
-      <c r="C57" s="1" t="inlineStr"/>
+      <c r="B57" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -960,8 +1296,14 @@
           <t>276634</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr"/>
-      <c r="C58" s="1" t="inlineStr"/>
+      <c r="B58" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
@@ -969,8 +1311,14 @@
           <t>276701</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr"/>
-      <c r="C59" s="1" t="inlineStr"/>
+      <c r="B59" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO -  AGUA, ESGOTO E SANEAMENTO</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -978,8 +1326,14 @@
           <t>277180</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr"/>
-      <c r="C60" s="1" t="inlineStr"/>
+      <c r="B60" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO -  AGUA, ESGOTO E SANEAMENTO</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -987,8 +1341,14 @@
           <t>277259</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr"/>
-      <c r="C61" s="1" t="inlineStr"/>
+      <c r="B61" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -996,8 +1356,14 @@
           <t>277323</t>
         </is>
       </c>
-      <c r="B62" s="1" t="inlineStr"/>
-      <c r="C62" s="1" t="inlineStr"/>
+      <c r="B62" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
@@ -1005,8 +1371,14 @@
           <t>277549</t>
         </is>
       </c>
-      <c r="B63" s="1" t="inlineStr"/>
-      <c r="C63" s="1" t="inlineStr"/>
+      <c r="B63" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
@@ -1014,8 +1386,14 @@
           <t>277596</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr"/>
-      <c r="C64" s="1" t="inlineStr"/>
+      <c r="B64" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -1023,8 +1401,14 @@
           <t>277977</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr"/>
-      <c r="C65" s="1" t="inlineStr"/>
+      <c r="B65" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
@@ -1032,8 +1416,14 @@
           <t>278213</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr"/>
-      <c r="C66" s="1" t="inlineStr"/>
+      <c r="B66" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
@@ -1041,8 +1431,14 @@
           <t>278240</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr"/>
-      <c r="C67" s="1" t="inlineStr"/>
+      <c r="B67" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
@@ -1050,8 +1446,14 @@
           <t>278306</t>
         </is>
       </c>
-      <c r="B68" s="1" t="inlineStr"/>
-      <c r="C68" s="1" t="inlineStr"/>
+      <c r="B68" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
@@ -1059,8 +1461,14 @@
           <t>278485</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr"/>
-      <c r="C69" s="1" t="inlineStr"/>
+      <c r="B69" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
@@ -1068,8 +1476,14 @@
           <t>278889</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr"/>
-      <c r="C70" s="1" t="inlineStr"/>
+      <c r="B70" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
@@ -1077,8 +1491,14 @@
           <t>279152</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr"/>
-      <c r="C71" s="1" t="inlineStr"/>
+      <c r="B71" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
@@ -1086,8 +1506,14 @@
           <t>279800</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr"/>
-      <c r="C72" s="1" t="inlineStr"/>
+      <c r="B72" s="1" t="inlineStr">
+        <is>
+          <t>B3 COMERCIAL - OUTROS SERVIÇOS E OUTRAS ATIVIDADES</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
@@ -1095,8 +1521,14 @@
           <t>279902</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr"/>
-      <c r="C73" s="1" t="inlineStr"/>
+      <c r="B73" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
@@ -1104,8 +1536,14 @@
           <t>279954</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr"/>
-      <c r="C74" s="1" t="inlineStr"/>
+      <c r="B74" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
@@ -1113,8 +1551,14 @@
           <t>280828</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr"/>
-      <c r="C75" s="1" t="inlineStr"/>
+      <c r="B75" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
@@ -1122,8 +1566,14 @@
           <t>280829</t>
         </is>
       </c>
-      <c r="B76" s="1" t="inlineStr"/>
-      <c r="C76" s="1" t="inlineStr"/>
+      <c r="B76" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
@@ -1131,8 +1581,14 @@
           <t>2831334</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr"/>
-      <c r="C77" s="1" t="inlineStr"/>
+      <c r="B77" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
@@ -1140,8 +1596,14 @@
           <t>2855065</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr"/>
-      <c r="C78" s="1" t="inlineStr"/>
+      <c r="B78" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
@@ -1149,8 +1611,14 @@
           <t>6010456</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr"/>
-      <c r="C79" s="1" t="inlineStr"/>
+      <c r="B79" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
@@ -1158,8 +1626,14 @@
           <t>8006557</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr"/>
-      <c r="C80" s="1" t="inlineStr"/>
+      <c r="B80" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
@@ -1167,8 +1641,14 @@
           <t>8010540</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr"/>
-      <c r="C81" s="1" t="inlineStr"/>
+      <c r="B81" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
@@ -1176,8 +1656,14 @@
           <t>9010310</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr"/>
-      <c r="C82" s="1" t="inlineStr"/>
+      <c r="B82" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO - MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1225,7 +1711,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>657</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -1238,7 +1724,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>789</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -1251,7 +1737,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>405</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -1264,7 +1750,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>116051</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
@@ -1277,7 +1763,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>841</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
@@ -1287,7 +1773,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>592</v>
+        <v>22</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>0</v>
@@ -1300,7 +1786,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>7679</v>
+        <v>22</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>0</v>
@@ -1313,7 +1799,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>534</v>
+        <v>22</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>0</v>
@@ -1326,7 +1812,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>0</v>
@@ -1339,7 +1825,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>903</v>
+        <v>22</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>0</v>
@@ -1352,7 +1838,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>591</v>
+        <v>22</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>0</v>
@@ -1365,7 +1851,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>1616</v>
+        <v>22</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>0</v>
@@ -1378,7 +1864,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>313</v>
+        <v>22</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>0</v>
@@ -1391,7 +1877,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>419</v>
+        <v>22</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>0</v>
@@ -1404,7 +1890,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>473</v>
+        <v>22</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>0</v>
@@ -1417,7 +1903,7 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>168</v>
+        <v>22</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>0</v>
@@ -1430,7 +1916,7 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>626</v>
+        <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>0</v>
@@ -1443,7 +1929,7 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>838</v>
+        <v>22</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>0</v>
@@ -1456,7 +1942,7 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>689</v>
+        <v>22</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>0</v>
@@ -1469,7 +1955,7 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>682</v>
+        <v>22</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>0</v>
@@ -1482,7 +1968,7 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>246</v>
+        <v>22</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>0</v>
@@ -1495,7 +1981,7 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>1048</v>
+        <v>22</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>0</v>
@@ -1508,7 +1994,7 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>0</v>
@@ -1521,7 +2007,7 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>247</v>
+        <v>22</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>0</v>
@@ -1534,7 +2020,7 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>1086</v>
+        <v>22</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>0</v>
@@ -1547,7 +2033,7 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>3539</v>
+        <v>22</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>0</v>
@@ -1560,7 +2046,7 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>0</v>
@@ -1573,7 +2059,7 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>4800</v>
+        <v>22</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>0</v>
@@ -1586,7 +2072,7 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>498</v>
+        <v>22</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>0</v>
@@ -1599,7 +2085,7 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>0</v>
@@ -1612,7 +2098,7 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>557</v>
+        <v>22</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>0</v>
@@ -1625,7 +2111,7 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>2840</v>
+        <v>22</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>0</v>
@@ -1638,7 +2124,7 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>525</v>
+        <v>22</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>0</v>
@@ -1651,7 +2137,7 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>1168</v>
+        <v>22</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>0</v>
@@ -1664,7 +2150,7 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>12652</v>
+        <v>22</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>0</v>
@@ -1677,7 +2163,7 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>351</v>
+        <v>22</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>0</v>
@@ -1690,7 +2176,7 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>150</v>
+        <v>22</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>0</v>
@@ -1703,7 +2189,7 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>89</v>
+        <v>22</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>0</v>
@@ -1716,7 +2202,7 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>1284</v>
+        <v>22</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>0</v>
@@ -1729,7 +2215,7 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>3236</v>
+        <v>22</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>0</v>
@@ -1742,7 +2228,7 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>225</v>
+        <v>22</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>0</v>
@@ -1755,7 +2241,7 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>968</v>
+        <v>22</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>0</v>
@@ -1768,7 +2254,7 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>134</v>
+        <v>22</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>0</v>
@@ -1781,7 +2267,7 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>2833</v>
+        <v>22</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>0</v>
@@ -1794,7 +2280,7 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>508</v>
+        <v>22</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>0</v>
@@ -1807,7 +2293,7 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>2580</v>
+        <v>22</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>0</v>
@@ -1820,7 +2306,7 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>1199</v>
+        <v>22</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>0</v>
@@ -1833,7 +2319,7 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>997</v>
+        <v>22</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>0</v>
@@ -1846,7 +2332,7 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>1126</v>
+        <v>22</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>0</v>
@@ -1859,7 +2345,7 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>669</v>
+        <v>22</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>0</v>
@@ -1872,7 +2358,7 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>0</v>
@@ -1885,7 +2371,7 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>641</v>
+        <v>22</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>0</v>
@@ -1898,7 +2384,7 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>406</v>
+        <v>22</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>0</v>
@@ -1911,7 +2397,7 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>1238</v>
+        <v>22</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>0</v>
@@ -1924,7 +2410,7 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>2194</v>
+        <v>22</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>0</v>
@@ -1937,7 +2423,7 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>1256</v>
+        <v>22</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>0</v>
@@ -1950,7 +2436,7 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>1989</v>
+        <v>22</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>0</v>
@@ -1963,7 +2449,7 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>1110</v>
+        <v>22</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>0</v>
@@ -1976,7 +2462,7 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>1053</v>
+        <v>22</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>0</v>
@@ -1989,7 +2475,7 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>522</v>
+        <v>22</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>0</v>
@@ -2002,7 +2488,7 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>1531</v>
+        <v>22</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>0</v>
@@ -2015,7 +2501,7 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>481</v>
+        <v>22</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>0</v>
@@ -2028,7 +2514,7 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>287</v>
+        <v>22</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>0</v>
@@ -2041,7 +2527,7 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>2893</v>
+        <v>22</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>0</v>
@@ -2054,7 +2540,7 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>812</v>
+        <v>22</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>0</v>
@@ -2067,7 +2553,7 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>651</v>
+        <v>22</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>0</v>
@@ -2080,7 +2566,7 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>265</v>
+        <v>22</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>0</v>
@@ -2093,7 +2579,7 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>979</v>
+        <v>22</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>0</v>
@@ -2106,7 +2592,7 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>1070</v>
+        <v>22</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>0</v>
@@ -2119,7 +2605,7 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>1125</v>
+        <v>22</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>0</v>
@@ -2132,7 +2618,7 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>849</v>
+        <v>22</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>0</v>
@@ -2145,7 +2631,7 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>1247</v>
+        <v>22</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>0</v>
@@ -2158,7 +2644,7 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>458</v>
+        <v>22</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>0</v>
@@ -2171,7 +2657,7 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>141</v>
+        <v>22</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>0</v>
@@ -2184,7 +2670,7 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>3093</v>
+        <v>22</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>0</v>
@@ -2197,7 +2683,7 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>1020</v>
+        <v>22</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>0</v>
@@ -2210,7 +2696,7 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>0</v>
@@ -2223,7 +2709,7 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>261</v>
+        <v>22</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>0</v>
@@ -2236,7 +2722,7 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>793</v>
+        <v>22</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>0</v>
@@ -2249,7 +2735,7 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>0</v>
@@ -2262,7 +2748,7 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>739</v>
+        <v>22</v>
       </c>
       <c r="C82" s="2" t="n">
         <v>0</v>

--- a/Leitor_de_Fatura/Faturas_Analaiser/Relatorio_Consolidado_NEOENERGIA_Texter.xlsx
+++ b/Leitor_de_Fatura/Faturas_Analaiser/Relatorio_Consolidado_NEOENERGIA_Texter.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Classificação" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Consumo_Faturado" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Consumo_Medido" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classificação" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consumo_Faturado" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consumo_Medido" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
